--- a/hardware/expansion-board-v4/CHECKLIST-V4.7.xlsx
+++ b/hardware/expansion-board-v4/CHECKLIST-V4.7.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V4.7 核对清单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="V4.7 核对清单" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'V4.7 核对清单'!$1:$1</definedName>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>134.4, 96.3</t>
+          <t>135.2, 96.8</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>134.3, 93.5</t>
+          <t>134.3, 93.8</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>110.7, 80.5</t>
+          <t>83.3, 85.6</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>129.3, 91.1</t>
+          <t>126.4, 90.7</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>136.2, 108.2</t>
+          <t>121.3, 100.8</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>120.5, 101.5</t>
+          <t>119.4, 100.1</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>128.2, 103.2</t>
+          <t>128.0, 102.1</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>130.0, 103.2</t>
+          <t>129.8, 102.1</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>131.8, 103.2</t>
+          <t>131.6, 102.1</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>100pF C0G</t>
+          <t>100nF</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>131.3, 100.1</t>
+          <t>133.6, 100.1</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>121.8, 98.7</t>
+          <t>122.0, 97.4</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>131.2, 97.9</t>
+          <t>131.1, 97.9</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="E170" s="10" t="inlineStr">
         <is>
-          <t>129.4, 89.0</t>
+          <t>126.4, 89.3</t>
         </is>
       </c>
       <c r="F170" s="12" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>121.9, 92.5</t>
+          <t>122.0, 91.0</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>121.9, 95.8</t>
+          <t>122.0, 93.9</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="E210" s="10" t="inlineStr">
         <is>
-          <t>133.8, 99.9</t>
+          <t>135.1, 102.5</t>
         </is>
       </c>
       <c r="F210" s="12" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>118.5, 84.7</t>
+          <t>118.3, 82.9</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>125.8, 89.2</t>
+          <t>124.4, 82.9</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">

--- a/hardware/expansion-board-v4/CHECKLIST-V4.7.xlsx
+++ b/hardware/expansion-board-v4/CHECKLIST-V4.7.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G246"/>
+  <dimension ref="A1:G247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>119.4, 100.1</t>
+          <t>117.2, 99.6</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -3268,46 +3268,46 @@
       </c>
       <c r="G95" s="5" t="inlineStr"/>
     </row>
-    <row r="96" ht="19" customHeight="1"/>
-    <row r="97" ht="19" customHeight="1">
-      <c r="A97" s="2" t="inlineStr"/>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>10k</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>R_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>55.2, 84.5</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>C 传感器 + GNSS</t>
-        </is>
-      </c>
-      <c r="G97" s="5" t="inlineStr"/>
-    </row>
+    <row r="96" ht="19" customHeight="1">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>C102</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>100nF</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>C_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>119.5, 100.7</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>G 航空波段 AIRBAND</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr"/>
+    </row>
+    <row r="97" ht="19" customHeight="1"/>
     <row r="98" ht="19" customHeight="1">
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>4.7k</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>64.1, 97.8</t>
+          <t>55.2, 84.5</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -3331,7 +3331,7 @@
       <c r="A99" s="2" t="inlineStr"/>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>64.1, 95.2</t>
+          <t>64.1, 97.8</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
@@ -3360,12 +3360,12 @@
       <c r="A100" s="2" t="inlineStr"/>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>4.7k</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>82.0, 69.1</t>
+          <t>64.1, 95.2</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>B MCU + Flash</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr"/>
@@ -3389,12 +3389,12 @@
       <c r="A101" s="2" t="inlineStr"/>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>80.0, 73.2</t>
+          <t>82.0, 69.1</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -3418,123 +3418,123 @@
       <c r="A102" s="2" t="inlineStr"/>
       <c r="B102" s="3" t="inlineStr">
         <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>80.0, 73.2</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>B MCU + Flash</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr"/>
+    </row>
+    <row r="103" ht="19" customHeight="1">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>10k</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
+      <c r="D103" s="4" t="inlineStr">
         <is>
           <t>R_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>87.9, 86.4</t>
         </is>
       </c>
-      <c r="F102" s="4" t="inlineStr">
+      <c r="F103" s="4" t="inlineStr">
         <is>
           <t>B MCU + Flash</t>
         </is>
       </c>
-      <c r="G102" s="5" t="inlineStr"/>
-    </row>
-    <row r="103" ht="19" customHeight="1">
-      <c r="A103" s="6" t="inlineStr"/>
-      <c r="B103" s="7" t="inlineStr">
-        <is>
-          <t>R7</t>
-        </is>
-      </c>
-      <c r="C103" s="8" t="inlineStr">
-        <is>
-          <t>5.1k DNP(带电源版)</t>
-        </is>
-      </c>
-      <c r="D103" s="8" t="inlineStr">
-        <is>
-          <t>R_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="inlineStr">
-        <is>
-          <t>141.4, 62.5</t>
-        </is>
-      </c>
-      <c r="F103" s="8" t="inlineStr">
-        <is>
-          <t>不贴（DNP）</t>
-        </is>
-      </c>
-      <c r="G103" s="9" t="inlineStr"/>
+      <c r="G103" s="5" t="inlineStr"/>
     </row>
     <row r="104" ht="19" customHeight="1">
       <c r="A104" s="6" t="inlineStr"/>
       <c r="B104" s="7" t="inlineStr">
         <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>5.1k DNP(带电源版)</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t>R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>141.4, 62.5</t>
+        </is>
+      </c>
+      <c r="F104" s="8" t="inlineStr">
+        <is>
+          <t>不贴（DNP）</t>
+        </is>
+      </c>
+      <c r="G104" s="9" t="inlineStr"/>
+    </row>
+    <row r="105" ht="19" customHeight="1">
+      <c r="A105" s="6" t="inlineStr"/>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="C104" s="8" t="inlineStr">
+      <c r="C105" s="8" t="inlineStr">
         <is>
           <t>5.1k DNP(带电源版)</t>
         </is>
       </c>
-      <c r="D104" s="8" t="inlineStr">
+      <c r="D105" s="8" t="inlineStr">
         <is>
           <t>R_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="E105" s="6" t="inlineStr">
         <is>
           <t>139.4, 62.5</t>
         </is>
       </c>
-      <c r="F104" s="8" t="inlineStr">
+      <c r="F105" s="8" t="inlineStr">
         <is>
           <t>不贴（DNP）</t>
         </is>
       </c>
-      <c r="G104" s="9" t="inlineStr"/>
-    </row>
-    <row r="105" ht="19" customHeight="1">
-      <c r="A105" s="2" t="inlineStr"/>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>27R</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>R_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>87.9, 83.3</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>B MCU + Flash</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr"/>
+      <c r="G105" s="9" t="inlineStr"/>
     </row>
     <row r="106" ht="19" customHeight="1">
       <c r="A106" s="2" t="inlineStr"/>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>85.3, 83.3</t>
+          <t>87.9, 83.3</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
@@ -3563,27 +3563,27 @@
       <c r="A107" s="2" t="inlineStr"/>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>3.32k</t>
+          <t>27R</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>105.1, 59.7</t>
+          <t>85.3, 83.3</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>B MCU + Flash</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr"/>
@@ -3592,27 +3592,27 @@
       <c r="A108" s="2" t="inlineStr"/>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>R17</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>3.32k</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>122.0, 97.4</t>
+          <t>105.1, 59.7</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr"/>
@@ -3621,7 +3621,7 @@
       <c r="A109" s="2" t="inlineStr"/>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>R17</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>91.4, 71.4</t>
+          <t>122.0, 97.4</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>D 978 收发</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr"/>
@@ -3650,22 +3650,22 @@
       <c r="A110" s="2" t="inlineStr"/>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>52.3R</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>115.1, 73.4</t>
+          <t>91.4, 71.4</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
@@ -3679,22 +3679,22 @@
       <c r="A111" s="2" t="inlineStr"/>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>R21</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>0R</t>
+          <t>52.3R</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>105.0, 72.6</t>
+          <t>115.1, 73.4</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
@@ -3708,7 +3708,7 @@
       <c r="A112" s="2" t="inlineStr"/>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>R21</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>100.3, 66.5</t>
+          <t>105.0, 72.6</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
@@ -3737,215 +3737,215 @@
       <c r="A113" s="2" t="inlineStr"/>
       <c r="B113" s="3" t="inlineStr">
         <is>
+          <t>R22</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>0R</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>100.3, 66.5</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>E 1090 接收链</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr"/>
+    </row>
+    <row r="114" ht="19" customHeight="1">
+      <c r="A114" s="2" t="inlineStr"/>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
           <t>R23</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C114" s="4" t="inlineStr">
         <is>
           <t>0R</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr">
+      <c r="D114" s="4" t="inlineStr">
         <is>
           <t>R_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>93.2, 77.2</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr">
+      <c r="F114" s="4" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G113" s="5" t="inlineStr"/>
-    </row>
-    <row r="114" ht="19" customHeight="1">
-      <c r="A114" s="6" t="inlineStr"/>
-      <c r="B114" s="7" t="inlineStr">
-        <is>
-          <t>R24</t>
-        </is>
-      </c>
-      <c r="C114" s="8" t="inlineStr">
-        <is>
-          <t>0R DNP(旁路外接)</t>
-        </is>
-      </c>
-      <c r="D114" s="8" t="inlineStr">
-        <is>
-          <t>R_0402_1005Metric</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>101.1, 63.1</t>
-        </is>
-      </c>
-      <c r="F114" s="8" t="inlineStr">
-        <is>
-          <t>不贴（DNP）</t>
-        </is>
-      </c>
-      <c r="G114" s="9" t="inlineStr"/>
+      <c r="G114" s="5" t="inlineStr"/>
     </row>
     <row r="115" ht="19" customHeight="1">
       <c r="A115" s="6" t="inlineStr"/>
       <c r="B115" s="7" t="inlineStr">
         <is>
+          <t>R24</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>0R DNP(旁路外接)</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t>R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>101.1, 63.1</t>
+        </is>
+      </c>
+      <c r="F115" s="8" t="inlineStr">
+        <is>
+          <t>不贴（DNP）</t>
+        </is>
+      </c>
+      <c r="G115" s="9" t="inlineStr"/>
+    </row>
+    <row r="116" ht="19" customHeight="1">
+      <c r="A116" s="6" t="inlineStr"/>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
           <t>R25</t>
         </is>
       </c>
-      <c r="C115" s="8" t="inlineStr">
+      <c r="C116" s="8" t="inlineStr">
         <is>
           <t>0R DNP(旁路板载)</t>
         </is>
       </c>
-      <c r="D115" s="8" t="inlineStr">
+      <c r="D116" s="8" t="inlineStr">
         <is>
           <t>R_0402_1005Metric</t>
         </is>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="E116" s="6" t="inlineStr">
         <is>
           <t>95.5, 62.9</t>
         </is>
       </c>
-      <c r="F115" s="8" t="inlineStr">
+      <c r="F116" s="8" t="inlineStr">
         <is>
           <t>不贴（DNP）</t>
         </is>
       </c>
-      <c r="G115" s="9" t="inlineStr"/>
-    </row>
-    <row r="116" ht="19" customHeight="1">
-      <c r="A116" s="2" t="inlineStr"/>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>R26</t>
-        </is>
-      </c>
-      <c r="C116" s="4" t="inlineStr">
-        <is>
-          <t>10k</t>
-        </is>
-      </c>
-      <c r="D116" s="4" t="inlineStr">
-        <is>
-          <t>R_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>67.3, 73.7</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>C 传感器 + GNSS</t>
-        </is>
-      </c>
-      <c r="G116" s="5" t="inlineStr"/>
+      <c r="G116" s="9" t="inlineStr"/>
     </row>
     <row r="117" ht="19" customHeight="1">
       <c r="A117" s="2" t="inlineStr"/>
       <c r="B117" s="3" t="inlineStr">
         <is>
+          <t>R26</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>67.3, 73.7</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>C 传感器 + GNSS</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr"/>
+    </row>
+    <row r="118" ht="19" customHeight="1">
+      <c r="A118" s="2" t="inlineStr"/>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
           <t>R27</t>
         </is>
       </c>
-      <c r="C117" s="4" t="inlineStr">
+      <c r="C118" s="4" t="inlineStr">
         <is>
           <t>10k</t>
         </is>
       </c>
-      <c r="D117" s="4" t="inlineStr">
+      <c r="D118" s="4" t="inlineStr">
         <is>
           <t>R_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>67.3, 71.1</t>
         </is>
       </c>
-      <c r="F117" s="4" t="inlineStr">
+      <c r="F118" s="4" t="inlineStr">
         <is>
           <t>C 传感器 + GNSS</t>
         </is>
       </c>
-      <c r="G117" s="5" t="inlineStr"/>
-    </row>
-    <row r="118" ht="19" customHeight="1">
-      <c r="A118" s="6" t="inlineStr"/>
-      <c r="B118" s="7" t="inlineStr">
+      <c r="G118" s="5" t="inlineStr"/>
+    </row>
+    <row r="119" ht="19" customHeight="1">
+      <c r="A119" s="6" t="inlineStr"/>
+      <c r="B119" s="7" t="inlineStr">
         <is>
           <t>R30</t>
         </is>
       </c>
-      <c r="C118" s="8" t="inlineStr">
+      <c r="C119" s="8" t="inlineStr">
         <is>
           <t>1k DNP</t>
         </is>
       </c>
-      <c r="D118" s="8" t="inlineStr">
+      <c r="D119" s="8" t="inlineStr">
         <is>
           <t>R_0402_1005Metric</t>
         </is>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="E119" s="6" t="inlineStr">
         <is>
           <t>96.8, 77.2</t>
         </is>
       </c>
-      <c r="F118" s="8" t="inlineStr">
+      <c r="F119" s="8" t="inlineStr">
         <is>
           <t>不贴（DNP）</t>
         </is>
       </c>
-      <c r="G118" s="9" t="inlineStr"/>
-    </row>
-    <row r="119" ht="19" customHeight="1">
-      <c r="A119" s="2" t="inlineStr"/>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>R31</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="inlineStr">
-        <is>
-          <t>1k</t>
-        </is>
-      </c>
-      <c r="D119" s="4" t="inlineStr">
-        <is>
-          <t>R_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>101.6, 75.7</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>E 1090 接收链</t>
-        </is>
-      </c>
-      <c r="G119" s="5" t="inlineStr"/>
+      <c r="G119" s="9" t="inlineStr"/>
     </row>
     <row r="120" ht="19" customHeight="1">
       <c r="A120" s="2" t="inlineStr"/>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R31</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>104.9, 75.7</t>
+          <t>101.6, 75.7</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
@@ -3969,12 +3969,12 @@
       <c r="A121" s="2" t="inlineStr"/>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>R33</t>
+          <t>R32</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>100k</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>100.9, 82.7</t>
+          <t>104.9, 75.7</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
@@ -3998,12 +3998,12 @@
       <c r="A122" s="2" t="inlineStr"/>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>R34</t>
+          <t>R33</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>100k</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>77.0, 73.2</t>
+          <t>100.9, 82.7</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
@@ -4027,99 +4027,99 @@
       <c r="A123" s="2" t="inlineStr"/>
       <c r="B123" s="3" t="inlineStr">
         <is>
+          <t>R34</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>77.0, 73.2</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>E 1090 接收链</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr"/>
+    </row>
+    <row r="124" ht="19" customHeight="1">
+      <c r="A124" s="2" t="inlineStr"/>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
           <t>R35</t>
         </is>
       </c>
-      <c r="C123" s="4" t="inlineStr">
+      <c r="C124" s="4" t="inlineStr">
         <is>
           <t>10k</t>
         </is>
       </c>
-      <c r="D123" s="4" t="inlineStr">
+      <c r="D124" s="4" t="inlineStr">
         <is>
           <t>R_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>77.0, 78.4</t>
         </is>
       </c>
-      <c r="F123" s="4" t="inlineStr">
+      <c r="F124" s="4" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G123" s="5" t="inlineStr"/>
-    </row>
-    <row r="124" ht="19" customHeight="1">
-      <c r="A124" s="6" t="inlineStr"/>
-      <c r="B124" s="7" t="inlineStr">
+      <c r="G124" s="5" t="inlineStr"/>
+    </row>
+    <row r="125" ht="19" customHeight="1">
+      <c r="A125" s="6" t="inlineStr"/>
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>R36</t>
         </is>
       </c>
-      <c r="C124" s="8" t="inlineStr">
+      <c r="C125" s="8" t="inlineStr">
         <is>
           <t>1k DNP</t>
         </is>
       </c>
-      <c r="D124" s="8" t="inlineStr">
+      <c r="D125" s="8" t="inlineStr">
         <is>
           <t>R_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="E125" s="6" t="inlineStr">
         <is>
           <t>96.5, 81.8</t>
         </is>
       </c>
-      <c r="F124" s="8" t="inlineStr">
+      <c r="F125" s="8" t="inlineStr">
         <is>
           <t>不贴（DNP）</t>
         </is>
       </c>
-      <c r="G124" s="9" t="inlineStr"/>
-    </row>
-    <row r="125" ht="19" customHeight="1">
-      <c r="A125" s="2" t="inlineStr"/>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>R37</t>
-        </is>
-      </c>
-      <c r="C125" s="4" t="inlineStr">
-        <is>
-          <t>0R</t>
-        </is>
-      </c>
-      <c r="D125" s="4" t="inlineStr">
-        <is>
-          <t>R_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
-        <is>
-          <t>137.0, 66.4</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>A 电源</t>
-        </is>
-      </c>
-      <c r="G125" s="5" t="inlineStr"/>
+      <c r="G125" s="9" t="inlineStr"/>
     </row>
     <row r="126" ht="19" customHeight="1">
       <c r="A126" s="2" t="inlineStr"/>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>R38</t>
+          <t>R37</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>180R</t>
+          <t>0R</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>133.1, 88.2</t>
+          <t>137.0, 66.4</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
@@ -4143,12 +4143,12 @@
       <c r="A127" s="2" t="inlineStr"/>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>R39</t>
+          <t>R38</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>5.62k</t>
+          <t>180R</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>136.2, 88.2</t>
+          <t>133.1, 88.2</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
@@ -4172,12 +4172,12 @@
       <c r="A128" s="2" t="inlineStr"/>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>R40</t>
+          <t>R39</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>31.6k</t>
+          <t>5.62k</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>134.6, 88.2</t>
+          <t>136.2, 88.2</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
@@ -4201,12 +4201,12 @@
       <c r="A129" s="2" t="inlineStr"/>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>R41</t>
+          <t>R40</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>470k</t>
+          <t>31.6k</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>139.1, 98.6</t>
+          <t>134.6, 88.2</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
@@ -4230,12 +4230,12 @@
       <c r="A130" s="2" t="inlineStr"/>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>R42</t>
+          <t>R41</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>150k</t>
+          <t>470k</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>137.4, 98.6</t>
+          <t>139.1, 98.6</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
@@ -4259,12 +4259,12 @@
       <c r="A131" s="2" t="inlineStr"/>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>R43</t>
+          <t>R42</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>150k</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>127.5, 65.0</t>
+          <t>137.4, 98.6</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
@@ -4288,12 +4288,12 @@
       <c r="A132" s="2" t="inlineStr"/>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>R44</t>
+          <t>R43</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>137.0, 69.5</t>
+          <t>127.5, 65.0</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
@@ -4317,7 +4317,7 @@
       <c r="A133" s="2" t="inlineStr"/>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>R45</t>
+          <t>R44</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>129.2, 84.0</t>
+          <t>137.0, 69.5</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
@@ -4346,7 +4346,7 @@
       <c r="A134" s="2" t="inlineStr"/>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>R46</t>
+          <t>R45</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>129.2, 86.5</t>
+          <t>129.2, 84.0</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
@@ -4375,7 +4375,7 @@
       <c r="A135" s="2" t="inlineStr"/>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>R47</t>
+          <t>R46</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>98.5, 91.7</t>
+          <t>129.2, 86.5</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>A 电源</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr"/>
@@ -4404,12 +4404,12 @@
       <c r="A136" s="2" t="inlineStr"/>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>R48</t>
+          <t>R47</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>0R</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>126.8, 67.0</t>
+          <t>98.5, 91.7</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>A 电源</t>
+          <t>D 978 收发</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr"/>
@@ -4433,7 +4433,7 @@
       <c r="A137" s="2" t="inlineStr"/>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>R49</t>
+          <t>R48</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>126.8, 69.4</t>
+          <t>126.8, 67.0</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
@@ -4462,12 +4462,12 @@
       <c r="A138" s="2" t="inlineStr"/>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>R50</t>
+          <t>R49</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>30k</t>
+          <t>0R</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -4477,12 +4477,12 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>86.5, 92.8</t>
+          <t>126.8, 69.4</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>B MCU + Flash</t>
+          <t>A 电源</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr"/>
@@ -4491,12 +4491,12 @@
       <c r="A139" s="2" t="inlineStr"/>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>R51</t>
+          <t>R50</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>30k</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>85.5, 88.5</t>
+          <t>86.5, 92.8</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
@@ -4520,7 +4520,7 @@
       <c r="A140" s="2" t="inlineStr"/>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>R52</t>
+          <t>R51</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -4530,17 +4530,17 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>64.4, 85.0</t>
+          <t>85.5, 88.5</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>B MCU + Flash</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr"/>
@@ -4549,7 +4549,7 @@
       <c r="A141" s="2" t="inlineStr"/>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>R53</t>
+          <t>R52</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>64.3, 83.0</t>
+          <t>64.4, 85.0</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
@@ -4578,12 +4578,12 @@
       <c r="A142" s="2" t="inlineStr"/>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>R54</t>
+          <t>R53</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>10R</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>116.5, 77.0</t>
+          <t>64.3, 83.0</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr"/>
@@ -4607,27 +4607,27 @@
       <c r="A143" s="2" t="inlineStr"/>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>R55</t>
+          <t>R54</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>10R</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>57.4, 89.8</t>
+          <t>116.5, 77.0</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr"/>
@@ -4636,7 +4636,7 @@
       <c r="A144" s="2" t="inlineStr"/>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>R56</t>
+          <t>R55</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>98.5, 90.0</t>
+          <t>57.4, 89.8</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr"/>
@@ -4665,12 +4665,12 @@
       <c r="A145" s="2" t="inlineStr"/>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>R57</t>
+          <t>R56</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>33R</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>104.0, 82.5</t>
+          <t>98.5, 90.0</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>D 978 收发</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr"/>
@@ -4694,12 +4694,12 @@
       <c r="A146" s="2" t="inlineStr"/>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>R58</t>
+          <t>R57</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>33R</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>132.5, 108.2</t>
+          <t>104.0, 82.5</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>G 航空波段 AIRBAND</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr"/>
@@ -4723,7 +4723,7 @@
       <c r="A147" s="2" t="inlineStr"/>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>R59</t>
+          <t>R58</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>132.5, 105.6</t>
+          <t>132.5, 108.2</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
@@ -4752,12 +4752,12 @@
       <c r="A148" s="2" t="inlineStr"/>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>R60</t>
+          <t>R59</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>0R</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>124.0, 101.5</t>
+          <t>132.5, 105.6</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
@@ -4781,71 +4781,71 @@
       <c r="A149" s="2" t="inlineStr"/>
       <c r="B149" s="3" t="inlineStr">
         <is>
+          <t>R60</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>0R</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>124.0, 101.5</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>G 航空波段 AIRBAND</t>
+        </is>
+      </c>
+      <c r="G149" s="5" t="inlineStr"/>
+    </row>
+    <row r="150" ht="19" customHeight="1">
+      <c r="A150" s="2" t="inlineStr"/>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
           <t>R61</t>
         </is>
       </c>
-      <c r="C149" s="4" t="inlineStr">
+      <c r="C150" s="4" t="inlineStr">
         <is>
           <t>10k</t>
         </is>
       </c>
-      <c r="D149" s="4" t="inlineStr">
+      <c r="D150" s="4" t="inlineStr">
         <is>
           <t>R_0402_1005Metric</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>131.1, 97.9</t>
         </is>
       </c>
-      <c r="F149" s="4" t="inlineStr">
+      <c r="F150" s="4" t="inlineStr">
         <is>
           <t>G 航空波段 AIRBAND</t>
         </is>
       </c>
-      <c r="G149" s="5" t="inlineStr"/>
-    </row>
-    <row r="150" ht="19" customHeight="1"/>
-    <row r="151" ht="19" customHeight="1">
-      <c r="A151" s="2" t="inlineStr"/>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>18nH 0402CS-18NXGRW</t>
-        </is>
-      </c>
-      <c r="D151" s="4" t="inlineStr">
-        <is>
-          <t>L_0402_1005Metric</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>110.4, 59.8</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>E 1090 接收链</t>
-        </is>
-      </c>
-      <c r="G151" s="5" t="inlineStr"/>
-    </row>
+      <c r="G150" s="5" t="inlineStr"/>
+    </row>
+    <row r="151" ht="19" customHeight="1"/>
     <row r="152" ht="19" customHeight="1">
       <c r="A152" s="2" t="inlineStr"/>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>33nH</t>
+          <t>18nH 0402CS-18NXGRW</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>57.7, 75.4</t>
+          <t>110.4, 59.8</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr"/>
@@ -4869,27 +4869,27 @@
       <c r="A153" s="2" t="inlineStr"/>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>L7</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>6.8uH</t>
+          <t>33nH</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>L_0805_2012Metric</t>
+          <t>L_0402_1005Metric</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>97.3, 94.7</t>
+          <t>57.7, 75.4</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr"/>
@@ -4898,22 +4898,22 @@
       <c r="A154" s="2" t="inlineStr"/>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>L8</t>
+          <t>L7</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>100nH</t>
+          <t>6.8uH</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>L_0402_1005Metric</t>
+          <t>L_0805_2012Metric</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>119.3, 90.3</t>
+          <t>97.3, 94.7</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
@@ -4927,12 +4927,12 @@
       <c r="A155" s="2" t="inlineStr"/>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L8</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>7.5nH</t>
+          <t>100nH</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>112.3, 94.8</t>
+          <t>119.3, 90.3</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
@@ -4956,12 +4956,12 @@
       <c r="A156" s="2" t="inlineStr"/>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>L10</t>
+          <t>L9</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>27nH</t>
+          <t>7.5nH</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>110.9, 95.7</t>
+          <t>112.3, 94.8</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
@@ -4985,12 +4985,12 @@
       <c r="A157" s="2" t="inlineStr"/>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>L11</t>
+          <t>L10</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>6.8nH</t>
+          <t>27nH</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>118.2, 97.5</t>
+          <t>110.9, 95.7</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
@@ -5014,7 +5014,7 @@
       <c r="A158" s="2" t="inlineStr"/>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>L12</t>
+          <t>L11</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>118.2, 95.2</t>
+          <t>118.2, 97.5</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
@@ -5043,12 +5043,12 @@
       <c r="A159" s="2" t="inlineStr"/>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>L13</t>
+          <t>L12</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>7.5nH</t>
+          <t>6.8nH</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>110.7, 92.2</t>
+          <t>118.2, 95.2</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
@@ -5072,12 +5072,12 @@
       <c r="A160" s="2" t="inlineStr"/>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>L14</t>
+          <t>L13</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>100nH</t>
+          <t>7.5nH</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>101.1, 70.6</t>
+          <t>110.7, 92.2</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>D 978 收发</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr"/>
@@ -5101,12 +5101,12 @@
       <c r="A161" s="2" t="inlineStr"/>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>L15</t>
+          <t>L14</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>33nH</t>
+          <t>100nH</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>57.6, 68.7</t>
+          <t>101.1, 70.6</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr"/>
@@ -5130,27 +5130,27 @@
       <c r="A162" s="2" t="inlineStr"/>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>L16</t>
+          <t>L15</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>1uH</t>
+          <t>33nH</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>L_Bourns-SRN4018</t>
+          <t>L_0402_1005Metric</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>139.7, 83.6</t>
+          <t>57.6, 68.7</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>A 电源</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr"/>
@@ -5159,22 +5159,22 @@
       <c r="A163" s="2" t="inlineStr"/>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>L17</t>
+          <t>L16</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>4.7uH XEL4030-472MEC</t>
+          <t>1uH</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>L_Coilcraft_XxL4030</t>
+          <t>L_Bourns-SRN4018</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>144.8, 95.0</t>
+          <t>139.7, 83.6</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
@@ -5188,66 +5188,66 @@
       <c r="A164" s="2" t="inlineStr"/>
       <c r="B164" s="3" t="inlineStr">
         <is>
+          <t>L17</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>4.7uH XEL4030-472MEC</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>L_Coilcraft_XxL4030</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>144.8, 95.0</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>A 电源</t>
+        </is>
+      </c>
+      <c r="G164" s="5" t="inlineStr"/>
+    </row>
+    <row r="165" ht="19" customHeight="1">
+      <c r="A165" s="2" t="inlineStr"/>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
           <t>L18</t>
         </is>
       </c>
-      <c r="C164" s="4" t="inlineStr">
+      <c r="C165" s="4" t="inlineStr">
         <is>
           <t>100nH</t>
         </is>
       </c>
-      <c r="D164" s="4" t="inlineStr">
+      <c r="D165" s="4" t="inlineStr">
         <is>
           <t>L_0402_1005Metric</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>126.0, 93.9</t>
         </is>
       </c>
-      <c r="F164" s="4" t="inlineStr">
+      <c r="F165" s="4" t="inlineStr">
         <is>
           <t>G 航空波段 AIRBAND</t>
         </is>
       </c>
-      <c r="G164" s="5" t="inlineStr"/>
-    </row>
-    <row r="165" ht="19" customHeight="1"/>
-    <row r="166" ht="19" customHeight="1">
-      <c r="A166" s="2" t="inlineStr"/>
-      <c r="B166" s="3" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="C166" s="4" t="inlineStr">
-        <is>
-          <t>TPESD8L3.3 0.3pFtyp 0.5pFmax</t>
-        </is>
-      </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>D_0402_1005Metric</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>101.1, 72.6</t>
-        </is>
-      </c>
-      <c r="F166" s="4" t="inlineStr">
-        <is>
-          <t>E 1090 接收链</t>
-        </is>
-      </c>
-      <c r="G166" s="5" t="inlineStr"/>
-    </row>
+      <c r="G165" s="5" t="inlineStr"/>
+    </row>
+    <row r="166" ht="19" customHeight="1"/>
     <row r="167" ht="19" customHeight="1">
       <c r="A167" s="2" t="inlineStr"/>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -5262,12 +5262,12 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>117.5, 89.9</t>
+          <t>101.1, 72.6</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr"/>
@@ -5276,7 +5276,7 @@
       <c r="A168" s="2" t="inlineStr"/>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>139.3, 75.4</t>
+          <t>117.5, 89.9</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>B MCU + Flash</t>
+          <t>D 978 收发</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr"/>
@@ -5305,99 +5305,99 @@
       <c r="A169" s="2" t="inlineStr"/>
       <c r="B169" s="3" t="inlineStr">
         <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>TPESD8L3.3 0.3pFtyp 0.5pFmax</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>D_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>139.3, 75.4</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>B MCU + Flash</t>
+        </is>
+      </c>
+      <c r="G169" s="5" t="inlineStr"/>
+    </row>
+    <row r="170" ht="19" customHeight="1">
+      <c r="A170" s="2" t="inlineStr"/>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="C169" s="4" t="inlineStr">
+      <c r="C170" s="4" t="inlineStr">
         <is>
           <t>TPESD8L3.3 0.3pFtyp 0.5pFmax</t>
         </is>
       </c>
-      <c r="D169" s="4" t="inlineStr">
+      <c r="D170" s="4" t="inlineStr">
         <is>
           <t>D_0402_1005Metric</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>139.3, 77.8</t>
         </is>
       </c>
-      <c r="F169" s="4" t="inlineStr">
+      <c r="F170" s="4" t="inlineStr">
         <is>
           <t>B MCU + Flash</t>
         </is>
       </c>
-      <c r="G169" s="5" t="inlineStr"/>
-    </row>
-    <row r="170" ht="19" customHeight="1">
-      <c r="A170" s="10" t="inlineStr"/>
-      <c r="B170" s="11" t="inlineStr">
+      <c r="G170" s="5" t="inlineStr"/>
+    </row>
+    <row r="171" ht="19" customHeight="1">
+      <c r="A171" s="10" t="inlineStr"/>
+      <c r="B171" s="11" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="C170" s="12" t="inlineStr">
+      <c r="C171" s="12" t="inlineStr">
         <is>
           <t>TPESD8L3.3 0.3pFtyp 0.5pFmax</t>
         </is>
       </c>
-      <c r="D170" s="12" t="inlineStr">
+      <c r="D171" s="12" t="inlineStr">
         <is>
           <t>D_0402_1005Metric</t>
         </is>
       </c>
-      <c r="E170" s="10" t="inlineStr">
+      <c r="E171" s="10" t="inlineStr">
         <is>
           <t>126.4, 89.3</t>
         </is>
       </c>
-      <c r="F170" s="12" t="inlineStr">
+      <c r="F171" s="12" t="inlineStr">
         <is>
           <t>G 航空波段 AIRBAND</t>
         </is>
       </c>
-      <c r="G170" s="13" t="inlineStr">
+      <c r="G171" s="13" t="inlineStr">
         <is>
           <t>有极性，认阴极标记带</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="19" customHeight="1"/>
-    <row r="172" ht="19" customHeight="1">
-      <c r="A172" s="2" t="inlineStr"/>
-      <c r="B172" s="3" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="C172" s="4" t="inlineStr">
-        <is>
-          <t>6V/200mA</t>
-        </is>
-      </c>
-      <c r="D172" s="4" t="inlineStr">
-        <is>
-          <t>Fuse_0805_2012Metric</t>
-        </is>
-      </c>
-      <c r="E172" s="2" t="inlineStr">
-        <is>
-          <t>122.0, 91.0</t>
-        </is>
-      </c>
-      <c r="F172" s="4" t="inlineStr">
-        <is>
-          <t>D 978 收发</t>
-        </is>
-      </c>
-      <c r="G172" s="5" t="inlineStr"/>
-    </row>
+    <row r="172" ht="19" customHeight="1"/>
     <row r="173" ht="19" customHeight="1">
       <c r="A173" s="2" t="inlineStr"/>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>98.3, 71.7</t>
+          <t>122.0, 91.0</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>D 978 收发</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr"/>
@@ -5426,7 +5426,7 @@
       <c r="A174" s="2" t="inlineStr"/>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>60.3, 75.9</t>
+          <t>98.3, 71.7</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr"/>
@@ -5455,66 +5455,66 @@
       <c r="A175" s="2" t="inlineStr"/>
       <c r="B175" s="3" t="inlineStr">
         <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>6V/200mA</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>Fuse_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>60.3, 75.9</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>C 传感器 + GNSS</t>
+        </is>
+      </c>
+      <c r="G175" s="5" t="inlineStr"/>
+    </row>
+    <row r="176" ht="19" customHeight="1">
+      <c r="A176" s="2" t="inlineStr"/>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
           <t>F5</t>
         </is>
       </c>
-      <c r="C175" s="4" t="inlineStr">
+      <c r="C176" s="4" t="inlineStr">
         <is>
           <t>6V/200mA</t>
         </is>
       </c>
-      <c r="D175" s="4" t="inlineStr">
+      <c r="D176" s="4" t="inlineStr">
         <is>
           <t>Fuse_0805_2012Metric</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>60.3, 69.2</t>
         </is>
       </c>
-      <c r="F175" s="4" t="inlineStr">
+      <c r="F176" s="4" t="inlineStr">
         <is>
           <t>C 传感器 + GNSS</t>
         </is>
       </c>
-      <c r="G175" s="5" t="inlineStr"/>
-    </row>
-    <row r="176" ht="19" customHeight="1"/>
-    <row r="177" ht="19" customHeight="1">
-      <c r="A177" s="2" t="inlineStr"/>
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C177" s="4" t="inlineStr">
-        <is>
-          <t>AO3401A</t>
-        </is>
-      </c>
-      <c r="D177" s="4" t="inlineStr">
-        <is>
-          <t>SOT-23</t>
-        </is>
-      </c>
-      <c r="E177" s="2" t="inlineStr">
-        <is>
-          <t>122.0, 93.9</t>
-        </is>
-      </c>
-      <c r="F177" s="4" t="inlineStr">
-        <is>
-          <t>D 978 收发</t>
-        </is>
-      </c>
-      <c r="G177" s="5" t="inlineStr"/>
-    </row>
+      <c r="G176" s="5" t="inlineStr"/>
+    </row>
+    <row r="177" ht="19" customHeight="1"/>
     <row r="178" ht="19" customHeight="1">
       <c r="A178" s="2" t="inlineStr"/>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>95.3, 71.7</t>
+          <t>122.0, 93.9</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>D 978 收发</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr"/>
@@ -5543,7 +5543,7 @@
       <c r="A179" s="2" t="inlineStr"/>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>63.5, 75.9</t>
+          <t>95.3, 71.7</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr"/>
@@ -5572,75 +5572,71 @@
       <c r="A180" s="2" t="inlineStr"/>
       <c r="B180" s="3" t="inlineStr">
         <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>AO3401A</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>63.5, 75.9</t>
+        </is>
+      </c>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>C 传感器 + GNSS</t>
+        </is>
+      </c>
+      <c r="G180" s="5" t="inlineStr"/>
+    </row>
+    <row r="181" ht="19" customHeight="1">
+      <c r="A181" s="2" t="inlineStr"/>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="C180" s="4" t="inlineStr">
+      <c r="C181" s="4" t="inlineStr">
         <is>
           <t>AO3401A</t>
         </is>
       </c>
-      <c r="D180" s="4" t="inlineStr">
+      <c r="D181" s="4" t="inlineStr">
         <is>
           <t>SOT-23</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>63.5, 69.2</t>
         </is>
       </c>
-      <c r="F180" s="4" t="inlineStr">
+      <c r="F181" s="4" t="inlineStr">
         <is>
           <t>C 传感器 + GNSS</t>
         </is>
       </c>
-      <c r="G180" s="5" t="inlineStr"/>
-    </row>
-    <row r="181" ht="19" customHeight="1"/>
-    <row r="182" ht="19" customHeight="1">
-      <c r="A182" s="10" t="inlineStr"/>
-      <c r="B182" s="11" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="C182" s="12" t="inlineStr">
-        <is>
-          <t>ME6211C33M5</t>
-        </is>
-      </c>
-      <c r="D182" s="12" t="inlineStr">
-        <is>
-          <t>SOT-23-5</t>
-        </is>
-      </c>
-      <c r="E182" s="10" t="inlineStr">
-        <is>
-          <t>74.7, 97.8</t>
-        </is>
-      </c>
-      <c r="F182" s="12" t="inlineStr">
-        <is>
-          <t>A 电源</t>
-        </is>
-      </c>
-      <c r="G182" s="13" t="inlineStr">
-        <is>
-          <t>认 pin1（缺角/圆点）</t>
-        </is>
-      </c>
-    </row>
+      <c r="G181" s="5" t="inlineStr"/>
+    </row>
+    <row r="182" ht="19" customHeight="1"/>
     <row r="183" ht="19" customHeight="1">
       <c r="A183" s="10" t="inlineStr"/>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>TPS7A2033PDBVR</t>
+          <t>ME6211C33M5</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
@@ -5650,7 +5646,7 @@
       </c>
       <c r="E183" s="10" t="inlineStr">
         <is>
-          <t>82.3, 97.8</t>
+          <t>74.7, 97.8</t>
         </is>
       </c>
       <c r="F183" s="12" t="inlineStr">
@@ -5668,7 +5664,7 @@
       <c r="A184" s="10" t="inlineStr"/>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="C184" s="12" t="inlineStr">
@@ -5683,7 +5679,7 @@
       </c>
       <c r="E184" s="10" t="inlineStr">
         <is>
-          <t>89.2, 97.8</t>
+          <t>82.3, 97.8</t>
         </is>
       </c>
       <c r="F184" s="12" t="inlineStr">
@@ -5701,27 +5697,27 @@
       <c r="A185" s="10" t="inlineStr"/>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>BNO085</t>
+          <t>TPS7A2033PDBVR</t>
         </is>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>BNO085_LGA-28</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="E185" s="10" t="inlineStr">
         <is>
-          <t>59.7, 84.5</t>
+          <t>89.2, 97.8</t>
         </is>
       </c>
       <c r="F185" s="12" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>A 电源</t>
         </is>
       </c>
       <c r="G185" s="13" t="inlineStr">
@@ -5734,22 +5730,22 @@
       <c r="A186" s="10" t="inlineStr"/>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="C186" s="12" t="inlineStr">
         <is>
-          <t>BMP388</t>
+          <t>BNO085</t>
         </is>
       </c>
       <c r="D186" s="12" t="inlineStr">
         <is>
-          <t>BMP388_LGA-10</t>
+          <t>BNO085_LGA-28</t>
         </is>
       </c>
       <c r="E186" s="10" t="inlineStr">
         <is>
-          <t>61.0, 88.9</t>
+          <t>59.7, 84.5</t>
         </is>
       </c>
       <c r="F186" s="12" t="inlineStr">
@@ -5767,22 +5763,22 @@
       <c r="A187" s="10" t="inlineStr"/>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>QMC5883P</t>
+          <t>BMP388</t>
         </is>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>LGA-16_3x3mm_P0.5mm</t>
+          <t>BMP388_LGA-10</t>
         </is>
       </c>
       <c r="E187" s="10" t="inlineStr">
         <is>
-          <t>59.7, 96.5</t>
+          <t>61.0, 88.9</t>
         </is>
       </c>
       <c r="F187" s="12" t="inlineStr">
@@ -5800,22 +5796,22 @@
       <c r="A188" s="10" t="inlineStr"/>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="C188" s="12" t="inlineStr">
         <is>
-          <t>ATGM336H-6N-74</t>
+          <t>QMC5883P</t>
         </is>
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>ATGM336H_LCC-18</t>
+          <t>LGA-16_3x3mm_P0.5mm</t>
         </is>
       </c>
       <c r="E188" s="10" t="inlineStr">
         <is>
-          <t>73.7, 89.1</t>
+          <t>59.7, 96.5</t>
         </is>
       </c>
       <c r="F188" s="12" t="inlineStr">
@@ -5833,27 +5829,27 @@
       <c r="A189" s="10" t="inlineStr"/>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>RP2040</t>
+          <t>ATGM336H-6N-74</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>QFN-56-1EP_7x7mm_P0.4mm_EP3.2x3.2mm</t>
+          <t>ATGM336H_LCC-18</t>
         </is>
       </c>
       <c r="E189" s="10" t="inlineStr">
         <is>
-          <t>86.4, 76.9</t>
+          <t>73.7, 89.1</t>
         </is>
       </c>
       <c r="F189" s="12" t="inlineStr">
         <is>
-          <t>B MCU + Flash</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G189" s="13" t="inlineStr">
@@ -5866,22 +5862,22 @@
       <c r="A190" s="10" t="inlineStr"/>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="C190" s="12" t="inlineStr">
         <is>
-          <t>W25Q128JVSIQ</t>
+          <t>RP2040</t>
         </is>
       </c>
       <c r="D190" s="12" t="inlineStr">
         <is>
-          <t>SOIC-8_5.3x5.3mm_P1.27mm</t>
+          <t>QFN-56-1EP_7x7mm_P0.4mm_EP3.2x3.2mm</t>
         </is>
       </c>
       <c r="E190" s="10" t="inlineStr">
         <is>
-          <t>93.7, 85.9</t>
+          <t>86.4, 76.9</t>
         </is>
       </c>
       <c r="F190" s="12" t="inlineStr">
@@ -5899,27 +5895,27 @@
       <c r="A191" s="10" t="inlineStr"/>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>CC1312R1F3RGZR</t>
+          <t>W25Q128JVSIQ</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>QFN-48-1EP_7x7mm_P0.5mm_EP5.15x5.15mm</t>
+          <t>SOIC-8_5.3x5.3mm_P1.27mm</t>
         </is>
       </c>
       <c r="E191" s="10" t="inlineStr">
         <is>
-          <t>104.5, 92.0</t>
+          <t>93.7, 85.9</t>
         </is>
       </c>
       <c r="F191" s="12" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>B MCU + Flash</t>
         </is>
       </c>
       <c r="G191" s="13" t="inlineStr">
@@ -5932,27 +5928,27 @@
       <c r="A192" s="10" t="inlineStr"/>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="C192" s="12" t="inlineStr">
         <is>
-          <t>QPL9547TR7</t>
+          <t>CC1312R1F3RGZR</t>
         </is>
       </c>
       <c r="D192" s="12" t="inlineStr">
         <is>
-          <t>DFN-8-1EP_2x2mm_P0.5mm_EP0.86x1.55mm</t>
+          <t>QFN-48-1EP_7x7mm_P0.5mm_EP5.15x5.15mm</t>
         </is>
       </c>
       <c r="E192" s="10" t="inlineStr">
         <is>
-          <t>107.7, 61.9</t>
+          <t>104.5, 92.0</t>
         </is>
       </c>
       <c r="F192" s="12" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>D 978 收发</t>
         </is>
       </c>
       <c r="G192" s="13" t="inlineStr">
@@ -5965,22 +5961,22 @@
       <c r="A193" s="10" t="inlineStr"/>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>BGA2817</t>
+          <t>QPL9547TR7</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>SOT-363_SC-70-6</t>
+          <t>DFN-8-1EP_2x2mm_P0.5mm_EP0.86x1.55mm</t>
         </is>
       </c>
       <c r="E193" s="10" t="inlineStr">
         <is>
-          <t>117.1, 62.5</t>
+          <t>107.7, 61.9</t>
         </is>
       </c>
       <c r="F193" s="12" t="inlineStr">
@@ -5998,22 +5994,22 @@
       <c r="A194" s="10" t="inlineStr"/>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="C194" s="12" t="inlineStr">
         <is>
-          <t>AD8313ARMZ</t>
+          <t>BGA2817</t>
         </is>
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>MSOP-8_3x3mm_P0.65mm</t>
+          <t>SOT-363_SC-70-6</t>
         </is>
       </c>
       <c r="E194" s="10" t="inlineStr">
         <is>
-          <t>111.1, 73.4</t>
+          <t>117.1, 62.5</t>
         </is>
       </c>
       <c r="F194" s="12" t="inlineStr">
@@ -6031,22 +6027,22 @@
       <c r="A195" s="10" t="inlineStr"/>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>U15</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>TLV3501(TOKMAS)</t>
+          <t>AD8313ARMZ</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>SOT-23-6</t>
+          <t>MSOP-8_3x3mm_P0.65mm</t>
         </is>
       </c>
       <c r="E195" s="10" t="inlineStr">
         <is>
-          <t>100.6, 79.5</t>
+          <t>111.1, 73.4</t>
         </is>
       </c>
       <c r="F195" s="12" t="inlineStr">
@@ -6064,22 +6060,22 @@
       <c r="A196" s="10" t="inlineStr"/>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U15</t>
         </is>
       </c>
       <c r="C196" s="12" t="inlineStr">
         <is>
-          <t>XA17-G4K</t>
+          <t>TLV3501(TOKMAS)</t>
         </is>
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>SOT-363_SC-70-6</t>
+          <t>SOT-23-6</t>
         </is>
       </c>
       <c r="E196" s="10" t="inlineStr">
         <is>
-          <t>98.0, 62.9</t>
+          <t>100.6, 79.5</t>
         </is>
       </c>
       <c r="F196" s="12" t="inlineStr">
@@ -6097,7 +6093,7 @@
       <c r="A197" s="10" t="inlineStr"/>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>U17</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
@@ -6112,12 +6108,12 @@
       </c>
       <c r="E197" s="10" t="inlineStr">
         <is>
-          <t>68.6, 78.1</t>
+          <t>98.0, 62.9</t>
         </is>
       </c>
       <c r="F197" s="12" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G197" s="13" t="inlineStr">
@@ -6130,27 +6126,27 @@
       <c r="A198" s="10" t="inlineStr"/>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U17</t>
         </is>
       </c>
       <c r="C198" s="12" t="inlineStr">
         <is>
-          <t>CH224K</t>
+          <t>XA17-G4K</t>
         </is>
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>CH224K_ESSOP-10</t>
+          <t>SOT-363_SC-70-6</t>
         </is>
       </c>
       <c r="E198" s="10" t="inlineStr">
         <is>
-          <t>132.5, 68.6</t>
+          <t>68.6, 78.1</t>
         </is>
       </c>
       <c r="F198" s="12" t="inlineStr">
         <is>
-          <t>A 电源</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G198" s="13" t="inlineStr">
@@ -6163,22 +6159,22 @@
       <c r="A199" s="10" t="inlineStr"/>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>U19</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>SY6970</t>
+          <t>CH224K</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm_ThermalVias</t>
+          <t>CH224K_ESSOP-10</t>
         </is>
       </c>
       <c r="E199" s="10" t="inlineStr">
         <is>
-          <t>134.5, 83.7</t>
+          <t>132.5, 68.6</t>
         </is>
       </c>
       <c r="F199" s="12" t="inlineStr">
@@ -6196,22 +6192,22 @@
       <c r="A200" s="10" t="inlineStr"/>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>U20</t>
+          <t>U19</t>
         </is>
       </c>
       <c r="C200" s="12" t="inlineStr">
         <is>
-          <t>SY7069</t>
+          <t>SY6970</t>
         </is>
       </c>
       <c r="D200" s="12" t="inlineStr">
         <is>
-          <t>TSOT-23-6</t>
+          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm_ThermalVias</t>
         </is>
       </c>
       <c r="E200" s="10" t="inlineStr">
         <is>
-          <t>139.2, 95.0</t>
+          <t>134.5, 83.7</t>
         </is>
       </c>
       <c r="F200" s="12" t="inlineStr">
@@ -6229,27 +6225,27 @@
       <c r="A201" s="10" t="inlineStr"/>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>U21</t>
+          <t>U20</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>BK4819QN32SC</t>
+          <t>SY7069</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>QFN-32-1EP_4x4mm_P0.4mm_EP2.65x2.65mm</t>
+          <t>TSOT-23-6</t>
         </is>
       </c>
       <c r="E201" s="10" t="inlineStr">
         <is>
-          <t>127.5, 97.6</t>
+          <t>139.2, 95.0</t>
         </is>
       </c>
       <c r="F201" s="12" t="inlineStr">
         <is>
-          <t>G 航空波段 AIRBAND</t>
+          <t>A 电源</t>
         </is>
       </c>
       <c r="G201" s="13" t="inlineStr">
@@ -6262,146 +6258,146 @@
       <c r="A202" s="10" t="inlineStr"/>
       <c r="B202" s="11" t="inlineStr">
         <is>
+          <t>U21</t>
+        </is>
+      </c>
+      <c r="C202" s="12" t="inlineStr">
+        <is>
+          <t>BK4819QN32SC</t>
+        </is>
+      </c>
+      <c r="D202" s="12" t="inlineStr">
+        <is>
+          <t>QFN-32-1EP_4x4mm_P0.4mm_EP2.65x2.65mm</t>
+        </is>
+      </c>
+      <c r="E202" s="10" t="inlineStr">
+        <is>
+          <t>127.5, 97.6</t>
+        </is>
+      </c>
+      <c r="F202" s="12" t="inlineStr">
+        <is>
+          <t>G 航空波段 AIRBAND</t>
+        </is>
+      </c>
+      <c r="G202" s="13" t="inlineStr">
+        <is>
+          <t>认 pin1（缺角/圆点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="19" customHeight="1">
+      <c r="A203" s="10" t="inlineStr"/>
+      <c r="B203" s="11" t="inlineStr">
+        <is>
           <t>U22</t>
         </is>
       </c>
-      <c r="C202" s="12" t="inlineStr">
+      <c r="C203" s="12" t="inlineStr">
         <is>
           <t>PCM1808PWR</t>
         </is>
       </c>
-      <c r="D202" s="12" t="inlineStr">
+      <c r="D203" s="12" t="inlineStr">
         <is>
           <t>TSSOP-14_4.4x5mm_P0.65mm</t>
         </is>
       </c>
-      <c r="E202" s="10" t="inlineStr">
+      <c r="E203" s="10" t="inlineStr">
         <is>
           <t>122.8, 105.3</t>
         </is>
       </c>
-      <c r="F202" s="12" t="inlineStr">
+      <c r="F203" s="12" t="inlineStr">
         <is>
           <t>G 航空波段 AIRBAND</t>
         </is>
       </c>
-      <c r="G202" s="13" t="inlineStr">
+      <c r="G203" s="13" t="inlineStr">
         <is>
           <t>认 pin1（缺角/圆点）</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="19" customHeight="1"/>
-    <row r="204" ht="19" customHeight="1">
-      <c r="A204" s="10" t="inlineStr"/>
-      <c r="B204" s="11" t="inlineStr">
-        <is>
-          <t>FL1</t>
-        </is>
-      </c>
-      <c r="C204" s="12" t="inlineStr">
-        <is>
-          <t>TA0970A</t>
-        </is>
-      </c>
-      <c r="D204" s="12" t="inlineStr">
-        <is>
-          <t>TA0970A_SMD3838-6</t>
-        </is>
-      </c>
-      <c r="E204" s="10" t="inlineStr">
-        <is>
-          <t>112.0, 65.5</t>
-        </is>
-      </c>
-      <c r="F204" s="12" t="inlineStr">
-        <is>
-          <t>E 1090 接收链</t>
-        </is>
-      </c>
-      <c r="G204" s="13" t="inlineStr">
-        <is>
-          <t>SAW 滤波器分输入输出，贴反不工作</t>
-        </is>
-      </c>
-    </row>
+    <row r="204" ht="19" customHeight="1"/>
     <row r="205" ht="19" customHeight="1">
       <c r="A205" s="10" t="inlineStr"/>
       <c r="B205" s="11" t="inlineStr">
         <is>
+          <t>FL1</t>
+        </is>
+      </c>
+      <c r="C205" s="12" t="inlineStr">
+        <is>
+          <t>TA0970A</t>
+        </is>
+      </c>
+      <c r="D205" s="12" t="inlineStr">
+        <is>
+          <t>TA0970A_SMD3838-6</t>
+        </is>
+      </c>
+      <c r="E205" s="10" t="inlineStr">
+        <is>
+          <t>112.0, 65.5</t>
+        </is>
+      </c>
+      <c r="F205" s="12" t="inlineStr">
+        <is>
+          <t>E 1090 接收链</t>
+        </is>
+      </c>
+      <c r="G205" s="13" t="inlineStr">
+        <is>
+          <t>SAW 滤波器分输入输出，贴反不工作</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="19" customHeight="1">
+      <c r="A206" s="10" t="inlineStr"/>
+      <c r="B206" s="11" t="inlineStr">
+        <is>
           <t>FL2</t>
         </is>
       </c>
-      <c r="C205" s="12" t="inlineStr">
+      <c r="C206" s="12" t="inlineStr">
         <is>
           <t>TA0970A</t>
         </is>
       </c>
-      <c r="D205" s="12" t="inlineStr">
+      <c r="D206" s="12" t="inlineStr">
         <is>
           <t>TA0970A_SMD3838-6</t>
         </is>
       </c>
-      <c r="E205" s="10" t="inlineStr">
+      <c r="E206" s="10" t="inlineStr">
         <is>
           <t>118.4, 66.5</t>
         </is>
       </c>
-      <c r="F205" s="12" t="inlineStr">
+      <c r="F206" s="12" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G205" s="13" t="inlineStr">
+      <c r="G206" s="13" t="inlineStr">
         <is>
           <t>SAW 滤波器分输入输出，贴反不工作</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="19" customHeight="1"/>
-    <row r="207" ht="19" customHeight="1">
-      <c r="A207" s="2" t="inlineStr"/>
-      <c r="B207" s="3" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="C207" s="4" t="inlineStr">
-        <is>
-          <t>12MHz CL=10pF ABM8-272-T3</t>
-        </is>
-      </c>
-      <c r="D207" s="4" t="inlineStr">
-        <is>
-          <t>Crystal_SMD_3225-4Pin_3.2x2.5mm</t>
-        </is>
-      </c>
-      <c r="E207" s="2" t="inlineStr">
-        <is>
-          <t>85.1, 69.1</t>
-        </is>
-      </c>
-      <c r="F207" s="4" t="inlineStr">
-        <is>
-          <t>B MCU + Flash</t>
-        </is>
-      </c>
-      <c r="G207" s="5" t="inlineStr">
-        <is>
-          <t>无源晶体，转 180° 等价，长边对长边即可</t>
-        </is>
-      </c>
-    </row>
+    <row r="207" ht="19" customHeight="1"/>
     <row r="208" ht="19" customHeight="1">
       <c r="A208" s="2" t="inlineStr"/>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>Y2</t>
+          <t>Y1</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>48MHz ABM8W-7pF</t>
+          <t>12MHz CL=10pF ABM8-272-T3</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
@@ -6411,12 +6407,12 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>108.3, 98.3</t>
+          <t>85.1, 69.1</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>B MCU + Flash</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
@@ -6429,119 +6425,123 @@
       <c r="A209" s="2" t="inlineStr"/>
       <c r="B209" s="3" t="inlineStr">
         <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>48MHz ABM8W-7pF</t>
+        </is>
+      </c>
+      <c r="D209" s="4" t="inlineStr">
+        <is>
+          <t>Crystal_SMD_3225-4Pin_3.2x2.5mm</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>108.3, 98.3</t>
+        </is>
+      </c>
+      <c r="F209" s="4" t="inlineStr">
+        <is>
+          <t>D 978 收发</t>
+        </is>
+      </c>
+      <c r="G209" s="5" t="inlineStr">
+        <is>
+          <t>无源晶体，转 180° 等价，长边对长边即可</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="19" customHeight="1">
+      <c r="A210" s="2" t="inlineStr"/>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="C209" s="4" t="inlineStr">
+      <c r="C210" s="4" t="inlineStr">
         <is>
           <t>32.768kHz FC-135</t>
         </is>
       </c>
-      <c r="D209" s="4" t="inlineStr">
+      <c r="D210" s="4" t="inlineStr">
         <is>
           <t>Crystal_SMD_3215-2Pin_3.2x1.5mm</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>111.6, 87.0</t>
         </is>
       </c>
-      <c r="F209" s="4" t="inlineStr">
+      <c r="F210" s="4" t="inlineStr">
         <is>
           <t>D 978 收发</t>
         </is>
       </c>
-      <c r="G209" s="5" t="inlineStr"/>
-    </row>
-    <row r="210" ht="19" customHeight="1">
-      <c r="A210" s="10" t="inlineStr"/>
-      <c r="B210" s="11" t="inlineStr">
+      <c r="G210" s="5" t="inlineStr"/>
+    </row>
+    <row r="211" ht="19" customHeight="1">
+      <c r="A211" s="10" t="inlineStr"/>
+      <c r="B211" s="11" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="C210" s="12" t="inlineStr">
+      <c r="C211" s="12" t="inlineStr">
         <is>
           <t>26MHz TCXO &lt;=2.5ppm</t>
         </is>
       </c>
-      <c r="D210" s="12" t="inlineStr">
+      <c r="D211" s="12" t="inlineStr">
         <is>
           <t>Crystal_SMD_2520-4Pin_2.5x2.0mm</t>
         </is>
       </c>
-      <c r="E210" s="10" t="inlineStr">
+      <c r="E211" s="10" t="inlineStr">
         <is>
           <t>135.1, 102.5</t>
         </is>
       </c>
-      <c r="F210" s="12" t="inlineStr">
+      <c r="F211" s="12" t="inlineStr">
         <is>
           <t>G 航空波段 AIRBAND</t>
         </is>
       </c>
-      <c r="G210" s="13" t="inlineStr">
+      <c r="G211" s="13" t="inlineStr">
         <is>
           <t>有源 TCXO：pin2=GND / pin4=Vcc，转 180° 直接短路、上电即烧。顶面无标记，倒角在底面 #1 角（手册 C0.2）——贴前翻过来认，或先用一颗定出「底面倒角↔顶面打标」的对应关系再批量贴；板上丝印的实心圆点指向 pin1</t>
         </is>
       </c>
     </row>
-    <row r="211" ht="19" customHeight="1"/>
-    <row r="212" ht="19" customHeight="1">
-      <c r="A212" s="2" t="inlineStr"/>
-      <c r="B212" s="3" t="inlineStr">
-        <is>
-          <t>J1</t>
-        </is>
-      </c>
-      <c r="C212" s="4" t="inlineStr">
-        <is>
-          <t>J3_HAT_2x20_SMD排针</t>
-        </is>
-      </c>
-      <c r="D212" s="4" t="inlineStr">
-        <is>
-          <t>PinHeader_2x20_P2.54mm_Vertical_SMD</t>
-        </is>
-      </c>
-      <c r="E212" s="2" t="inlineStr">
-        <is>
-          <t>92.6, 106.3</t>
-        </is>
-      </c>
-      <c r="F212" s="4" t="inlineStr">
-        <is>
-          <t>F 对外接口</t>
-        </is>
-      </c>
-      <c r="G212" s="5" t="inlineStr"/>
-    </row>
+    <row r="212" ht="19" customHeight="1"/>
     <row r="213" ht="19" customHeight="1">
       <c r="A213" s="2" t="inlineStr"/>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>U.FL_GNSS_EXT(经尾线转SMA)</t>
+          <t>J3_HAT_2x20_SMD排针</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
+          <t>PinHeader_2x20_P2.54mm_Vertical_SMD</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>54.0, 75.9</t>
+          <t>92.6, 106.3</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>F 对外接口</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr"/>
@@ -6550,27 +6550,27 @@
       <c r="A214" s="2" t="inlineStr"/>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>USB-C_16P</t>
+          <t>U.FL_GNSS_EXT(经尾线转SMA)</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>USB_C_Receptacle_HRO_TYPE-C-31-M-12</t>
+          <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>145.8, 73.0</t>
+          <t>54.0, 75.9</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>B MCU + Flash</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr"/>
@@ -6579,27 +6579,27 @@
       <c r="A215" s="2" t="inlineStr"/>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>J5</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>U.FL_978</t>
+          <t>USB-C_16P</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
+          <t>USB_C_Receptacle_HRO_TYPE-C-31-M-12</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>118.3, 82.9</t>
+          <t>145.8, 73.0</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>D 978 收发</t>
+          <t>B MCU + Flash</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr"/>
@@ -6608,12 +6608,12 @@
       <c r="A216" s="2" t="inlineStr"/>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>J6</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>U.FL_1090_EXT(经尾线转SMA)</t>
+          <t>U.FL_978</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>106.5, 67.3</t>
+          <t>118.3, 82.9</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>E 1090 接收链</t>
+          <t>D 978 收发</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr"/>
@@ -6637,12 +6637,12 @@
       <c r="A217" s="2" t="inlineStr"/>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>J7</t>
+          <t>J6</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>U.FL_IFA_TEST(π后调试口)</t>
+          <t>U.FL_1090_EXT(经尾线转SMA)</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>90.0, 61.3</t>
+          <t>106.5, 67.3</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
@@ -6666,12 +6666,12 @@
       <c r="A218" s="2" t="inlineStr"/>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>J8</t>
+          <t>J7</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>U.FL→内置patch</t>
+          <t>U.FL_IFA_TEST(π后调试口)</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>54.0, 69.2</t>
+          <t>90.0, 61.3</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>C 传感器 + GNSS</t>
+          <t>E 1090 接收链</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr"/>
@@ -6695,27 +6695,27 @@
       <c r="A219" s="2" t="inlineStr"/>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>J9</t>
+          <t>J8</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>MX1.25WT-2P BAT</t>
+          <t>U.FL→内置patch</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>MX1.25WT-2P_1x02-1MP_P1.25mm_Horizontal</t>
+          <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>144.8, 99.0</t>
+          <t>54.0, 69.2</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>A 电源</t>
+          <t>C 传感器 + GNSS</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr"/>
@@ -6724,289 +6724,289 @@
       <c r="A220" s="2" t="inlineStr"/>
       <c r="B220" s="3" t="inlineStr">
         <is>
+          <t>J9</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>MX1.25WT-2P BAT</t>
+        </is>
+      </c>
+      <c r="D220" s="4" t="inlineStr">
+        <is>
+          <t>MX1.25WT-2P_1x02-1MP_P1.25mm_Horizontal</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>144.8, 99.0</t>
+        </is>
+      </c>
+      <c r="F220" s="4" t="inlineStr">
+        <is>
+          <t>A 电源</t>
+        </is>
+      </c>
+      <c r="G220" s="5" t="inlineStr"/>
+    </row>
+    <row r="221" ht="19" customHeight="1">
+      <c r="A221" s="2" t="inlineStr"/>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
           <t>J10</t>
         </is>
       </c>
-      <c r="C220" s="4" t="inlineStr">
+      <c r="C221" s="4" t="inlineStr">
         <is>
           <t>U.FL_VHF(经尾线转SMA)</t>
         </is>
       </c>
-      <c r="D220" s="4" t="inlineStr">
+      <c r="D221" s="4" t="inlineStr">
         <is>
           <t>U.FL_Hirose_U.FL-R-SMT-1_Vertical</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>124.4, 82.9</t>
         </is>
       </c>
-      <c r="F220" s="4" t="inlineStr">
+      <c r="F221" s="4" t="inlineStr">
         <is>
           <t>G 航空波段 AIRBAND</t>
         </is>
       </c>
-      <c r="G220" s="5" t="inlineStr"/>
-    </row>
-    <row r="221" ht="19" customHeight="1"/>
-    <row r="222" ht="19" customHeight="1">
-      <c r="A222" s="6" t="inlineStr"/>
-      <c r="B222" s="7" t="inlineStr">
+      <c r="G221" s="5" t="inlineStr"/>
+    </row>
+    <row r="222" ht="19" customHeight="1"/>
+    <row r="223" ht="19" customHeight="1">
+      <c r="A223" s="6" t="inlineStr"/>
+      <c r="B223" s="7" t="inlineStr">
         <is>
           <t>ANT1</t>
         </is>
       </c>
-      <c r="C222" s="8" t="inlineStr">
+      <c r="C223" s="8" t="inlineStr">
         <is>
           <t>IFA_1090</t>
         </is>
       </c>
-      <c r="D222" s="8" t="inlineStr">
+      <c r="D223" s="8" t="inlineStr">
         <is>
           <t>ANT_IFA_1090MHz</t>
         </is>
       </c>
-      <c r="E222" s="6" t="inlineStr">
+      <c r="E223" s="6" t="inlineStr">
         <is>
           <t>79.2, 57.8</t>
         </is>
       </c>
-      <c r="F222" s="8" t="inlineStr">
+      <c r="F223" s="8" t="inlineStr">
         <is>
           <t>不贴（板载天线）</t>
         </is>
       </c>
-      <c r="G222" s="9" t="inlineStr">
+      <c r="G223" s="9" t="inlineStr">
         <is>
           <t>50.0mm外包络/48.5mm中心线；V4.0装盒实测1082.5MHz、SWR 1.09</t>
         </is>
       </c>
     </row>
-    <row r="223" ht="19" customHeight="1"/>
-    <row r="224" ht="19" customHeight="1">
-      <c r="A224" s="6" t="inlineStr"/>
-      <c r="B224" s="7" t="inlineStr">
-        <is>
-          <t>ZP1</t>
-        </is>
-      </c>
-      <c r="C224" s="8" t="inlineStr">
-        <is>
-          <t>DNP 并-天线侧</t>
-        </is>
-      </c>
-      <c r="D224" s="8" t="inlineStr">
-        <is>
-          <t>C_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="E224" s="6" t="inlineStr">
-        <is>
-          <t>79.2, 63.6</t>
-        </is>
-      </c>
-      <c r="F224" s="8" t="inlineStr">
-        <is>
-          <t>不贴（DNP）</t>
-        </is>
-      </c>
-      <c r="G224" s="9" t="inlineStr">
-        <is>
-          <t>默认DNP；V4.0实测直通状态</t>
-        </is>
-      </c>
-    </row>
+    <row r="224" ht="19" customHeight="1"/>
     <row r="225" ht="19" customHeight="1">
       <c r="A225" s="6" t="inlineStr"/>
       <c r="B225" s="7" t="inlineStr">
         <is>
+          <t>ZP1</t>
+        </is>
+      </c>
+      <c r="C225" s="8" t="inlineStr">
+        <is>
+          <t>DNP 并-天线侧</t>
+        </is>
+      </c>
+      <c r="D225" s="8" t="inlineStr">
+        <is>
+          <t>C_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="E225" s="6" t="inlineStr">
+        <is>
+          <t>79.2, 63.6</t>
+        </is>
+      </c>
+      <c r="F225" s="8" t="inlineStr">
+        <is>
+          <t>不贴（DNP）</t>
+        </is>
+      </c>
+      <c r="G225" s="9" t="inlineStr">
+        <is>
+          <t>默认DNP；V4.0实测直通状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="19" customHeight="1">
+      <c r="A226" s="6" t="inlineStr"/>
+      <c r="B226" s="7" t="inlineStr">
+        <is>
           <t>ZP2</t>
         </is>
       </c>
-      <c r="C225" s="8" t="inlineStr">
+      <c r="C226" s="8" t="inlineStr">
         <is>
           <t>DNP 并-电台侧</t>
         </is>
       </c>
-      <c r="D225" s="8" t="inlineStr">
+      <c r="D226" s="8" t="inlineStr">
         <is>
           <t>C_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="E226" s="6" t="inlineStr">
         <is>
           <t>84.2, 63.6</t>
         </is>
       </c>
-      <c r="F225" s="8" t="inlineStr">
+      <c r="F226" s="8" t="inlineStr">
         <is>
           <t>不贴（DNP）</t>
         </is>
       </c>
-      <c r="G225" s="9" t="inlineStr">
+      <c r="G226" s="9" t="inlineStr">
         <is>
           <t>默认DNP；历史HFSS 3.3pF仅作异常复调备选</t>
         </is>
       </c>
     </row>
-    <row r="226" ht="19" customHeight="1"/>
-    <row r="227" ht="19" customHeight="1">
-      <c r="A227" s="2" t="inlineStr"/>
-      <c r="B227" s="3" t="inlineStr">
+    <row r="227" ht="19" customHeight="1"/>
+    <row r="228" ht="19" customHeight="1">
+      <c r="A228" s="2" t="inlineStr"/>
+      <c r="B228" s="3" t="inlineStr">
         <is>
           <t>ZS1</t>
         </is>
       </c>
-      <c r="C227" s="4" t="inlineStr">
+      <c r="C228" s="4" t="inlineStr">
         <is>
           <t>0R 串</t>
         </is>
       </c>
-      <c r="D227" s="4" t="inlineStr">
+      <c r="D228" s="4" t="inlineStr">
         <is>
           <t>L_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>81.7, 62.9</t>
         </is>
       </c>
-      <c r="F227" s="4" t="inlineStr">
+      <c r="F228" s="4" t="inlineStr">
         <is>
           <t>E 1090 接收链</t>
         </is>
       </c>
-      <c r="G227" s="5" t="inlineStr">
+      <c r="G228" s="5" t="inlineStr">
         <is>
           <t>默认0R直通；V4.0实测即为此状态</t>
         </is>
       </c>
     </row>
-    <row r="228" ht="19" customHeight="1"/>
-    <row r="229" ht="19" customHeight="1">
-      <c r="A229" s="6" t="inlineStr"/>
-      <c r="B229" s="7" t="inlineStr">
-        <is>
-          <t>SW1</t>
-        </is>
-      </c>
-      <c r="C229" s="8" t="inlineStr">
-        <is>
-          <t>RESET短接焊盘</t>
-        </is>
-      </c>
-      <c r="D229" s="8" t="inlineStr">
-        <is>
-          <t>SolderJumper-2_P1.3mm_Open_Pad1.0x1.5mm</t>
-        </is>
-      </c>
-      <c r="E229" s="6" t="inlineStr">
-        <is>
-          <t>51.9, 77.5</t>
-        </is>
-      </c>
-      <c r="F229" s="8" t="inlineStr">
-        <is>
-          <t>不贴（短接焊盘）</t>
-        </is>
-      </c>
-      <c r="G229" s="9" t="inlineStr"/>
-    </row>
+    <row r="229" ht="19" customHeight="1"/>
     <row r="230" ht="19" customHeight="1">
       <c r="A230" s="6" t="inlineStr"/>
       <c r="B230" s="7" t="inlineStr">
         <is>
+          <t>SW1</t>
+        </is>
+      </c>
+      <c r="C230" s="8" t="inlineStr">
+        <is>
+          <t>RESET短接焊盘</t>
+        </is>
+      </c>
+      <c r="D230" s="8" t="inlineStr">
+        <is>
+          <t>SolderJumper-2_P1.3mm_Open_Pad1.0x1.5mm</t>
+        </is>
+      </c>
+      <c r="E230" s="6" t="inlineStr">
+        <is>
+          <t>51.9, 77.5</t>
+        </is>
+      </c>
+      <c r="F230" s="8" t="inlineStr">
+        <is>
+          <t>不贴（短接焊盘）</t>
+        </is>
+      </c>
+      <c r="G230" s="9" t="inlineStr"/>
+    </row>
+    <row r="231" ht="19" customHeight="1">
+      <c r="A231" s="6" t="inlineStr"/>
+      <c r="B231" s="7" t="inlineStr">
+        <is>
           <t>SW2</t>
         </is>
       </c>
-      <c r="C230" s="8" t="inlineStr">
+      <c r="C231" s="8" t="inlineStr">
         <is>
           <t>BOOTSEL短接焊盘</t>
         </is>
       </c>
-      <c r="D230" s="8" t="inlineStr">
+      <c r="D231" s="8" t="inlineStr">
         <is>
           <t>SolderJumper-2_P1.3mm_Open_Pad1.0x1.5mm</t>
         </is>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="E231" s="6" t="inlineStr">
         <is>
           <t>51.9, 81.0</t>
         </is>
       </c>
-      <c r="F230" s="8" t="inlineStr">
+      <c r="F231" s="8" t="inlineStr">
         <is>
           <t>不贴（短接焊盘）</t>
         </is>
       </c>
-      <c r="G230" s="9" t="inlineStr"/>
-    </row>
-    <row r="231" ht="19" customHeight="1">
-      <c r="A231" s="2" t="inlineStr"/>
-      <c r="B231" s="3" t="inlineStr">
+      <c r="G231" s="9" t="inlineStr"/>
+    </row>
+    <row r="232" ht="19" customHeight="1">
+      <c r="A232" s="2" t="inlineStr"/>
+      <c r="B232" s="3" t="inlineStr">
         <is>
           <t>SW3</t>
         </is>
       </c>
-      <c r="C231" s="4" t="inlineStr">
+      <c r="C232" s="4" t="inlineStr">
         <is>
           <t>TS24CA</t>
         </is>
       </c>
-      <c r="D231" s="4" t="inlineStr">
+      <c r="D232" s="4" t="inlineStr">
         <is>
           <t>SW_TS24CA_2x4_SideAct</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>147.9, 89.1</t>
         </is>
       </c>
-      <c r="F231" s="4" t="inlineStr">
+      <c r="F232" s="4" t="inlineStr">
         <is>
           <t>A 电源</t>
         </is>
       </c>
-      <c r="G231" s="5" t="inlineStr"/>
-    </row>
-    <row r="232" ht="19" customHeight="1"/>
-    <row r="233" ht="19" customHeight="1">
-      <c r="A233" s="6" t="inlineStr"/>
-      <c r="B233" s="7" t="inlineStr">
-        <is>
-          <t>TP1</t>
-        </is>
-      </c>
-      <c r="C233" s="8" t="inlineStr">
-        <is>
-          <t>TestPoint</t>
-        </is>
-      </c>
-      <c r="D233" s="8" t="inlineStr">
-        <is>
-          <t>TestPoint_Pad_1.0x1.0mm</t>
-        </is>
-      </c>
-      <c r="E233" s="6" t="inlineStr">
-        <is>
-          <t>51.9, 86.0</t>
-        </is>
-      </c>
-      <c r="F233" s="8" t="inlineStr">
-        <is>
-          <t>不贴（测试点焊盘）</t>
-        </is>
-      </c>
-      <c r="G233" s="9" t="inlineStr"/>
-    </row>
+      <c r="G232" s="5" t="inlineStr"/>
+    </row>
+    <row r="233" ht="19" customHeight="1"/>
     <row r="234" ht="19" customHeight="1">
       <c r="A234" s="6" t="inlineStr"/>
       <c r="B234" s="7" t="inlineStr">
         <is>
-          <t>TP2</t>
+          <t>TP1</t>
         </is>
       </c>
       <c r="C234" s="8" t="inlineStr">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="E234" s="6" t="inlineStr">
         <is>
-          <t>51.9, 88.1</t>
+          <t>51.9, 86.0</t>
         </is>
       </c>
       <c r="F234" s="8" t="inlineStr">
@@ -7035,7 +7035,7 @@
       <c r="A235" s="6" t="inlineStr"/>
       <c r="B235" s="7" t="inlineStr">
         <is>
-          <t>TP3</t>
+          <t>TP2</t>
         </is>
       </c>
       <c r="C235" s="8" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="E235" s="6" t="inlineStr">
         <is>
-          <t>51.9, 90.1</t>
+          <t>51.9, 88.1</t>
         </is>
       </c>
       <c r="F235" s="8" t="inlineStr">
@@ -7064,7 +7064,7 @@
       <c r="A236" s="6" t="inlineStr"/>
       <c r="B236" s="7" t="inlineStr">
         <is>
-          <t>TP4</t>
+          <t>TP3</t>
         </is>
       </c>
       <c r="C236" s="8" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="E236" s="6" t="inlineStr">
         <is>
-          <t>51.9, 92.1</t>
+          <t>51.9, 90.1</t>
         </is>
       </c>
       <c r="F236" s="8" t="inlineStr">
@@ -7093,7 +7093,7 @@
       <c r="A237" s="6" t="inlineStr"/>
       <c r="B237" s="7" t="inlineStr">
         <is>
-          <t>TP5</t>
+          <t>TP4</t>
         </is>
       </c>
       <c r="C237" s="8" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="E237" s="6" t="inlineStr">
         <is>
-          <t>51.9, 94.2</t>
+          <t>51.9, 92.1</t>
         </is>
       </c>
       <c r="F237" s="8" t="inlineStr">
@@ -7122,7 +7122,7 @@
       <c r="A238" s="6" t="inlineStr"/>
       <c r="B238" s="7" t="inlineStr">
         <is>
-          <t>TP6</t>
+          <t>TP5</t>
         </is>
       </c>
       <c r="C238" s="8" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="E238" s="6" t="inlineStr">
         <is>
-          <t>51.9, 96.2</t>
+          <t>51.9, 94.2</t>
         </is>
       </c>
       <c r="F238" s="8" t="inlineStr">
@@ -7151,66 +7151,66 @@
       <c r="A239" s="6" t="inlineStr"/>
       <c r="B239" s="7" t="inlineStr">
         <is>
+          <t>TP6</t>
+        </is>
+      </c>
+      <c r="C239" s="8" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="D239" s="8" t="inlineStr">
+        <is>
+          <t>TestPoint_Pad_1.0x1.0mm</t>
+        </is>
+      </c>
+      <c r="E239" s="6" t="inlineStr">
+        <is>
+          <t>51.9, 96.2</t>
+        </is>
+      </c>
+      <c r="F239" s="8" t="inlineStr">
+        <is>
+          <t>不贴（测试点焊盘）</t>
+        </is>
+      </c>
+      <c r="G239" s="9" t="inlineStr"/>
+    </row>
+    <row r="240" ht="19" customHeight="1">
+      <c r="A240" s="6" t="inlineStr"/>
+      <c r="B240" s="7" t="inlineStr">
+        <is>
           <t>TP7</t>
         </is>
       </c>
-      <c r="C239" s="8" t="inlineStr">
+      <c r="C240" s="8" t="inlineStr">
         <is>
           <t>TestPoint</t>
         </is>
       </c>
-      <c r="D239" s="8" t="inlineStr">
+      <c r="D240" s="8" t="inlineStr">
         <is>
           <t>TestPoint_Pad_1.0x1.0mm</t>
         </is>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="E240" s="6" t="inlineStr">
         <is>
           <t>51.9, 98.2</t>
         </is>
       </c>
-      <c r="F239" s="8" t="inlineStr">
+      <c r="F240" s="8" t="inlineStr">
         <is>
           <t>不贴（测试点焊盘）</t>
         </is>
       </c>
-      <c r="G239" s="9" t="inlineStr"/>
-    </row>
-    <row r="240" ht="19" customHeight="1"/>
-    <row r="241" ht="19" customHeight="1">
-      <c r="A241" s="6" t="inlineStr"/>
-      <c r="B241" s="7" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C241" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D241" s="8" t="inlineStr">
-        <is>
-          <t>MountingHole_2.7mm_M2.5</t>
-        </is>
-      </c>
-      <c r="E241" s="6" t="inlineStr">
-        <is>
-          <t>54.0, 56.0</t>
-        </is>
-      </c>
-      <c r="F241" s="8" t="inlineStr">
-        <is>
-          <t>不贴（安装孔）</t>
-        </is>
-      </c>
-      <c r="G241" s="9" t="inlineStr"/>
-    </row>
+      <c r="G240" s="9" t="inlineStr"/>
+    </row>
+    <row r="241" ht="19" customHeight="1"/>
     <row r="242" ht="19" customHeight="1">
       <c r="A242" s="6" t="inlineStr"/>
       <c r="B242" s="7" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C242" s="8" t="inlineStr">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="E242" s="6" t="inlineStr">
         <is>
-          <t>146.0, 56.0</t>
+          <t>54.0, 56.0</t>
         </is>
       </c>
       <c r="F242" s="8" t="inlineStr">
@@ -7239,7 +7239,7 @@
       <c r="A243" s="6" t="inlineStr"/>
       <c r="B243" s="7" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C243" s="8" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="E243" s="6" t="inlineStr">
         <is>
-          <t>54.0, 106.0</t>
+          <t>146.0, 56.0</t>
         </is>
       </c>
       <c r="F243" s="8" t="inlineStr">
@@ -7268,60 +7268,89 @@
       <c r="A244" s="6" t="inlineStr"/>
       <c r="B244" s="7" t="inlineStr">
         <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C244" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D244" s="8" t="inlineStr">
+        <is>
+          <t>MountingHole_2.7mm_M2.5</t>
+        </is>
+      </c>
+      <c r="E244" s="6" t="inlineStr">
+        <is>
+          <t>54.0, 106.0</t>
+        </is>
+      </c>
+      <c r="F244" s="8" t="inlineStr">
+        <is>
+          <t>不贴（安装孔）</t>
+        </is>
+      </c>
+      <c r="G244" s="9" t="inlineStr"/>
+    </row>
+    <row r="245" ht="19" customHeight="1">
+      <c r="A245" s="6" t="inlineStr"/>
+      <c r="B245" s="7" t="inlineStr">
+        <is>
           <t>H4</t>
         </is>
       </c>
-      <c r="C244" s="8" t="inlineStr">
+      <c r="C245" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D244" s="8" t="inlineStr">
+      <c r="D245" s="8" t="inlineStr">
         <is>
           <t>MountingHole_2.7mm_M2.5</t>
         </is>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="E245" s="6" t="inlineStr">
         <is>
           <t>146.0, 106.0</t>
         </is>
       </c>
-      <c r="F244" s="8" t="inlineStr">
+      <c r="F245" s="8" t="inlineStr">
         <is>
           <t>不贴（安装孔）</t>
         </is>
       </c>
-      <c r="G244" s="9" t="inlineStr"/>
-    </row>
-    <row r="245" ht="19" customHeight="1"/>
-    <row r="246" ht="19" customHeight="1">
-      <c r="A246" s="2" t="inlineStr"/>
-      <c r="B246" s="3" t="inlineStr">
+      <c r="G245" s="9" t="inlineStr"/>
+    </row>
+    <row r="246" ht="19" customHeight="1"/>
+    <row r="247" ht="19" customHeight="1">
+      <c r="A247" s="2" t="inlineStr"/>
+      <c r="B247" s="3" t="inlineStr">
         <is>
           <t>RT1</t>
         </is>
       </c>
-      <c r="C246" s="4" t="inlineStr">
+      <c r="C247" s="4" t="inlineStr">
         <is>
           <t>NCP18XH103F03RB 10k NTC</t>
         </is>
       </c>
-      <c r="D246" s="4" t="inlineStr">
+      <c r="D247" s="4" t="inlineStr">
         <is>
           <t>R_0603_1608Metric</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>54.8, 100.9</t>
         </is>
       </c>
-      <c r="F246" s="4" t="inlineStr">
+      <c r="F247" s="4" t="inlineStr">
         <is>
           <t>A 电源</t>
         </is>
       </c>
-      <c r="G246" s="5" t="inlineStr"/>
+      <c r="G247" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <printOptions gridLines="0"/>
